--- a/academias/Programación - Estadisticos 20212.xlsx
+++ b/academias/Programación - Estadisticos 20212.xlsx
@@ -566,25 +566,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>68.75</v>
+        <v>75</v>
       </c>
       <c r="H3" s="1">
-        <v>31.25</v>
+        <v>25</v>
       </c>
       <c r="I3" s="2">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K3" s="1">
-        <v>31.25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1742,25 +1742,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>68.75</v>
+        <v>75</v>
       </c>
       <c r="H3" s="1">
-        <v>31.25</v>
+        <v>25</v>
       </c>
       <c r="I3" s="2">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K3" s="1">
-        <v>31.25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:11">

--- a/academias/Programación - Estadisticos 20212.xlsx
+++ b/academias/Programación - Estadisticos 20212.xlsx
@@ -531,25 +531,25 @@
         <v>20</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H2" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -566,25 +566,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>75</v>
+        <v>90.63</v>
       </c>
       <c r="H3" s="1">
-        <v>25</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I3" s="2">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K3" s="1">
-        <v>25</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -601,25 +601,25 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>70.37</v>
+        <v>88.89</v>
       </c>
       <c r="H4" s="1">
-        <v>29.63</v>
+        <v>11.11</v>
       </c>
       <c r="I4" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K4" s="1">
-        <v>29.63</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -636,25 +636,25 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>77.78</v>
+        <v>92.59</v>
       </c>
       <c r="H5" s="1">
-        <v>22.22</v>
+        <v>7.41</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K5" s="1">
-        <v>22.22</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -671,25 +671,25 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>60.71</v>
+        <v>82.14</v>
       </c>
       <c r="H6" s="1">
-        <v>39.29</v>
+        <v>17.86</v>
       </c>
       <c r="I6" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K6" s="1">
-        <v>39.29</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -986,25 +986,25 @@
         <v>20</v>
       </c>
       <c r="E15">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1021,25 +1021,25 @@
         <v>20</v>
       </c>
       <c r="E16">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1056,25 +1056,25 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1143,22 +1143,25 @@
         <v>20</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.9</v>
       </c>
       <c r="J2">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1175,22 +1178,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I3" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J3">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1207,22 +1213,25 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>81.48</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>18.52</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.4</v>
       </c>
       <c r="J4">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1239,22 +1248,25 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>92.59</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>7.41</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1271,22 +1283,25 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>28.57</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.7</v>
       </c>
       <c r="J6">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1367,22 +1382,25 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.3</v>
       </c>
       <c r="J9">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1399,22 +1417,25 @@
         <v>28</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>3.57</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.1</v>
       </c>
       <c r="J10">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1431,22 +1452,25 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>92.86</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>7.14</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6.9</v>
       </c>
       <c r="J11">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1463,22 +1487,25 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>62.96</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>37.04</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.5</v>
       </c>
       <c r="J12">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>37.04</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1495,22 +1522,25 @@
         <v>24</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>37.5</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.7</v>
       </c>
       <c r="J13">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1527,22 +1557,25 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>79.17</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>20.83</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7.4</v>
       </c>
       <c r="J14">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1559,22 +1592,25 @@
         <v>20</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>7.9</v>
       </c>
       <c r="J15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1591,22 +1627,25 @@
         <v>20</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7.8</v>
       </c>
       <c r="J16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1623,22 +1662,25 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8.4</v>
       </c>
       <c r="J17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1707,25 +1749,25 @@
         <v>20</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H2" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1742,25 +1784,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>75</v>
+        <v>90.63</v>
       </c>
       <c r="H3" s="1">
-        <v>25</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I3" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K3" s="1">
-        <v>25</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1777,25 +1819,25 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>70.37</v>
+        <v>88.89</v>
       </c>
       <c r="H4" s="1">
-        <v>29.63</v>
+        <v>11.11</v>
       </c>
       <c r="I4" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K4" s="1">
-        <v>29.63</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1812,25 +1854,25 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>77.78</v>
+        <v>92.59</v>
       </c>
       <c r="H5" s="1">
-        <v>22.22</v>
+        <v>7.41</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K5" s="1">
-        <v>22.22</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1847,25 +1889,25 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>60.71</v>
+        <v>82.14</v>
       </c>
       <c r="H6" s="1">
-        <v>39.29</v>
+        <v>17.86</v>
       </c>
       <c r="I6" s="2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K6" s="1">
-        <v>39.29</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1952,19 +1994,19 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="H9" s="1">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="I9" s="2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1987,19 +2029,19 @@
         <v>28</v>
       </c>
       <c r="E10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>100</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="I10" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2022,19 +2064,19 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="I11" s="2">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2057,19 +2099,19 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>85.19</v>
+        <v>88.89</v>
       </c>
       <c r="H12" s="1">
-        <v>14.81</v>
+        <v>11.11</v>
       </c>
       <c r="I12" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2092,19 +2134,19 @@
         <v>24</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="H13" s="1">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="I13" s="2">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -2127,16 +2169,16 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>83.33</v>
+        <v>87.5</v>
       </c>
       <c r="H14" s="1">
-        <v>16.67</v>
+        <v>12.5</v>
       </c>
       <c r="I14" s="2">
         <v>7.4</v>
@@ -2162,25 +2204,25 @@
         <v>20</v>
       </c>
       <c r="E15">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2197,25 +2239,25 @@
         <v>20</v>
       </c>
       <c r="E16">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2232,25 +2274,25 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Programación - Estadisticos 20212.xlsx
+++ b/academias/Programación - Estadisticos 20212.xlsx
@@ -601,25 +601,25 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>88.89</v>
+        <v>92.59</v>
       </c>
       <c r="H4" s="1">
-        <v>11.11</v>
+        <v>7.41</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>11.11</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -671,25 +671,25 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>82.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>17.86</v>
+        <v>14.29</v>
       </c>
       <c r="I6" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6" s="1">
-        <v>17.86</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1213,25 +1213,25 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>81.48</v>
+        <v>92.59</v>
       </c>
       <c r="H4" s="1">
-        <v>18.52</v>
+        <v>7.41</v>
       </c>
       <c r="I4" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>18.52</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1283,25 +1283,25 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>71.43000000000001</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>28.57</v>
+        <v>21.43</v>
       </c>
       <c r="I6" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K6" s="1">
-        <v>28.57</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1318,22 +1318,25 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>58.33</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>41.67</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.5</v>
       </c>
       <c r="J7">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1350,22 +1353,25 @@
         <v>24</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>54.17</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>45.83</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.6</v>
       </c>
       <c r="J8">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1397,10 +1403,10 @@
         <v>7.3</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" s="1">
-        <v>12.5</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1487,25 +1493,25 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>62.96</v>
+        <v>92.59</v>
       </c>
       <c r="H12" s="1">
-        <v>37.04</v>
+        <v>7.41</v>
       </c>
       <c r="I12" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J12">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>37.04</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1522,25 +1528,25 @@
         <v>24</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="H13" s="1">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="I13" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K13" s="1">
-        <v>25</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1819,25 +1825,25 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>88.89</v>
+        <v>92.59</v>
       </c>
       <c r="H4" s="1">
-        <v>11.11</v>
+        <v>7.41</v>
       </c>
       <c r="I4" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>11.11</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1889,25 +1895,25 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>82.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>17.86</v>
+        <v>14.29</v>
       </c>
       <c r="I6" s="2">
         <v>7.3</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6" s="1">
-        <v>17.86</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2099,16 +2105,16 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>88.89</v>
+        <v>92.59</v>
       </c>
       <c r="H12" s="1">
-        <v>11.11</v>
+        <v>7.41</v>
       </c>
       <c r="I12" s="2">
         <v>7.3</v>

--- a/academias/Programación - Estadisticos 20212.xlsx
+++ b/academias/Programación - Estadisticos 20212.xlsx
@@ -601,25 +601,25 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H4" s="1">
-        <v>7.41</v>
+        <v>3.7</v>
       </c>
       <c r="I4" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -636,25 +636,25 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H5" s="1">
-        <v>7.41</v>
+        <v>3.7</v>
       </c>
       <c r="I5" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -671,25 +671,25 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>85.70999999999999</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>14.29</v>
+        <v>10.71</v>
       </c>
       <c r="I6" s="2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -718,13 +718,13 @@
         <v>16.67</v>
       </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -753,13 +753,13 @@
         <v>12.5</v>
       </c>
       <c r="I8" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1213,25 +1213,25 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H4" s="1">
-        <v>7.41</v>
+        <v>3.7</v>
       </c>
       <c r="I4" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1248,25 +1248,25 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H5" s="1">
-        <v>7.41</v>
+        <v>3.7</v>
       </c>
       <c r="I5" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1283,25 +1283,25 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>78.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>21.43</v>
+        <v>14.29</v>
       </c>
       <c r="I6" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>21.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1318,25 +1318,25 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>58.33</v>
+        <v>75</v>
       </c>
       <c r="H7" s="1">
-        <v>41.67</v>
+        <v>25</v>
       </c>
       <c r="I7" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1">
-        <v>37.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1353,25 +1353,25 @@
         <v>24</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>54.17</v>
+        <v>79.17</v>
       </c>
       <c r="H8" s="1">
-        <v>45.83</v>
+        <v>20.83</v>
       </c>
       <c r="I8" s="2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K8" s="1">
-        <v>41.67</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1400,13 +1400,13 @@
         <v>25</v>
       </c>
       <c r="I9" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1528,25 +1528,25 @@
         <v>24</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="H13" s="1">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="I13" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K13" s="1">
-        <v>20.83</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1825,25 +1825,25 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H4" s="1">
-        <v>7.41</v>
+        <v>3.7</v>
       </c>
       <c r="I4" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1860,25 +1860,25 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H5" s="1">
-        <v>7.41</v>
+        <v>3.7</v>
       </c>
       <c r="I5" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1907,13 +1907,13 @@
         <v>14.29</v>
       </c>
       <c r="I6" s="2">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1942,13 +1942,13 @@
         <v>16.67</v>
       </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1977,13 +1977,13 @@
         <v>12.5</v>
       </c>
       <c r="I8" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2035,19 +2035,19 @@
         <v>28</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>96.43000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H10" s="1">
-        <v>3.57</v>
+        <v>7.14</v>
       </c>
       <c r="I10" s="2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>7.14</v>
       </c>
       <c r="I11" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2210,19 +2210,19 @@
         <v>20</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I15" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2245,19 +2245,19 @@
         <v>20</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I16" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2280,19 +2280,19 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="I17" s="2">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>

--- a/academias/Programación - Estadisticos 20212.xlsx
+++ b/academias/Programación - Estadisticos 20212.xlsx
@@ -543,13 +543,13 @@
         <v>10</v>
       </c>
       <c r="I2" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -566,25 +566,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H3" s="1">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1155,13 +1155,13 @@
         <v>10</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1178,25 +1178,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H3" s="1">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="I3" s="2">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1755,25 +1755,25 @@
         <v>20</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H2" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I2" s="2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1790,25 +1790,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H3" s="1">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="I3" s="2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">

--- a/academias/Programación - Estadisticos 20212.xlsx
+++ b/academias/Programación - Estadisticos 20212.xlsx
@@ -931,10 +931,10 @@
         <v>6.3</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1318,25 +1318,25 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>75</v>
+        <v>79.17</v>
       </c>
       <c r="H7" s="1">
-        <v>25</v>
+        <v>20.83</v>
       </c>
       <c r="I7" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1353,25 +1353,25 @@
         <v>24</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>79.17</v>
+        <v>87.5</v>
       </c>
       <c r="H8" s="1">
-        <v>20.83</v>
+        <v>12.5</v>
       </c>
       <c r="I8" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1505,13 +1505,13 @@
         <v>7.41</v>
       </c>
       <c r="I12" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1540,13 +1540,13 @@
         <v>25</v>
       </c>
       <c r="I13" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1563,25 +1563,25 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>79.17</v>
+        <v>87.5</v>
       </c>
       <c r="H14" s="1">
-        <v>20.83</v>
+        <v>12.5</v>
       </c>
       <c r="I14" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1930,19 +1930,19 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="H7" s="1">
-        <v>16.67</v>
+        <v>8.33</v>
       </c>
       <c r="I7" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1965,19 +1965,19 @@
         <v>24</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>87.5</v>
+        <v>91.67</v>
       </c>
       <c r="H8" s="1">
-        <v>12.5</v>
+        <v>8.33</v>
       </c>
       <c r="I8" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2000,19 +2000,19 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2105,16 +2105,16 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H12" s="1">
-        <v>7.41</v>
+        <v>3.7</v>
       </c>
       <c r="I12" s="2">
         <v>7.3</v>
@@ -2140,25 +2140,25 @@
         <v>24</v>
       </c>
       <c r="E13">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>75</v>
+        <v>91.67</v>
       </c>
       <c r="H13" s="1">
-        <v>25</v>
+        <v>8.33</v>
       </c>
       <c r="I13" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2175,19 +2175,19 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J14">
         <v>0</v>
